--- a/data/matches_data.xlsx
+++ b/data/matches_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4B2842-B069-664F-A915-726BFB715B67}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1EE87E-6B04-9849-ABC7-6100150E0A65}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="460" windowWidth="24820" windowHeight="15020" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
@@ -16,6 +16,15 @@
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
     <sheet name="高級組_對賽安排" sheetId="3" r:id="rId2"/>
     <sheet name="中年組_對賽安排" sheetId="4" r:id="rId3"/>
+    <sheet name="元老組_對賽安排" sheetId="5" r:id="rId4"/>
+    <sheet name="初級組_對賽成績" sheetId="6" r:id="rId5"/>
+    <sheet name="高級組_對賽成績" sheetId="7" r:id="rId6"/>
+    <sheet name="中年組_對賽成績" sheetId="8" r:id="rId7"/>
+    <sheet name="元老組_對賽成績" sheetId="9" r:id="rId8"/>
+    <sheet name="初級組_積分榜" sheetId="10" r:id="rId9"/>
+    <sheet name="高級組_積分榜" sheetId="11" r:id="rId10"/>
+    <sheet name="中年組_積分榜" sheetId="12" r:id="rId11"/>
+    <sheet name="元老組_積分榜" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -2484,6 +2493,36 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3F7A55-04D4-B04B-84FF-591FF4F614D9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4AC8762-985C-3A44-B364-81DD41A51242}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D79C342-754F-004C-BF28-9C2A6F616F90}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A652382C-1B8E-3D47-8B07-5935E173CD82}">
   <dimension ref="A1"/>
@@ -2502,4 +2541,64 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47F9B54F-1C5B-D04D-993A-929D11ED7A52}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458C2E21-9836-DA4F-827E-3FCC599A483F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C9A1FC-F4CC-684F-B555-3819BBE99676}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{380B5DAA-237F-AA4C-8E6D-5F833856F631}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D35C9D81-3C0C-184B-A871-A36329AF0312}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F41BCBC-A307-E74C-9A70-3056FE7E3E56}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/matches_data.xlsx
+++ b/data/matches_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9BE618-95DB-DF44-A34C-E3792982B4F1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C03C3A-AF01-7A44-BE48-3ECD62D49348}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="116">
   <si>
     <t>日期</t>
   </si>
@@ -335,9 +335,6 @@
     <t>13/4 一</t>
   </si>
   <si>
-    <t>初 A1</t>
-  </si>
-  <si>
     <t>初 B</t>
   </si>
   <si>
@@ -378,12 +375,6 @@
   </si>
   <si>
     <t>初 O</t>
-  </si>
-  <si>
-    <t>初 A2</t>
-  </si>
-  <si>
-    <t>初 A3</t>
   </si>
   <si>
     <t>隊伍A</t>
@@ -391,6 +382,10 @@
   </si>
   <si>
     <t>隊伍B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初 A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -792,10 +787,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -826,7 +821,7 @@
         <v>81</v>
       </c>
       <c r="F2" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -843,7 +838,7 @@
         <v>81</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -860,7 +855,7 @@
         <v>81</v>
       </c>
       <c r="F4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -877,7 +872,7 @@
         <v>82</v>
       </c>
       <c r="F5" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -894,7 +889,7 @@
         <v>82</v>
       </c>
       <c r="F6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -911,7 +906,7 @@
         <v>82</v>
       </c>
       <c r="F7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -931,7 +926,7 @@
         <v>81</v>
       </c>
       <c r="F8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -948,7 +943,7 @@
         <v>81</v>
       </c>
       <c r="F9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -965,7 +960,7 @@
         <v>81</v>
       </c>
       <c r="F10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -982,7 +977,7 @@
         <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -999,7 +994,7 @@
         <v>82</v>
       </c>
       <c r="F12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1016,7 +1011,7 @@
         <v>82</v>
       </c>
       <c r="F13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1036,7 +1031,7 @@
         <v>81</v>
       </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1053,7 +1048,7 @@
         <v>81</v>
       </c>
       <c r="F15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1070,7 +1065,7 @@
         <v>81</v>
       </c>
       <c r="F16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1087,7 +1082,7 @@
         <v>82</v>
       </c>
       <c r="F17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1104,7 +1099,7 @@
         <v>82</v>
       </c>
       <c r="F18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1121,7 +1116,7 @@
         <v>82</v>
       </c>
       <c r="F19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1141,7 +1136,7 @@
         <v>81</v>
       </c>
       <c r="F20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1158,7 +1153,7 @@
         <v>81</v>
       </c>
       <c r="F21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1175,7 +1170,7 @@
         <v>81</v>
       </c>
       <c r="F22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1192,7 +1187,7 @@
         <v>82</v>
       </c>
       <c r="F23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1209,7 +1204,7 @@
         <v>82</v>
       </c>
       <c r="F24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1226,7 +1221,7 @@
         <v>82</v>
       </c>
       <c r="F25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1246,7 +1241,7 @@
         <v>81</v>
       </c>
       <c r="F26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1263,7 +1258,7 @@
         <v>81</v>
       </c>
       <c r="F27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1280,7 +1275,7 @@
         <v>81</v>
       </c>
       <c r="F28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1297,7 +1292,7 @@
         <v>82</v>
       </c>
       <c r="F29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1314,7 +1309,7 @@
         <v>82</v>
       </c>
       <c r="F30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1331,7 +1326,7 @@
         <v>82</v>
       </c>
       <c r="F31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1456,7 +1451,7 @@
         <v>81</v>
       </c>
       <c r="F38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1473,7 +1468,7 @@
         <v>81</v>
       </c>
       <c r="F39" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1490,7 +1485,7 @@
         <v>81</v>
       </c>
       <c r="F40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1507,7 +1502,7 @@
         <v>82</v>
       </c>
       <c r="F41" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1524,7 +1519,7 @@
         <v>82</v>
       </c>
       <c r="F42" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1541,7 +1536,7 @@
         <v>82</v>
       </c>
       <c r="F43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1561,7 +1556,7 @@
         <v>81</v>
       </c>
       <c r="F44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1578,7 +1573,7 @@
         <v>81</v>
       </c>
       <c r="F45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1595,7 +1590,7 @@
         <v>81</v>
       </c>
       <c r="F46" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1612,7 +1607,7 @@
         <v>82</v>
       </c>
       <c r="F47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1629,7 +1624,7 @@
         <v>82</v>
       </c>
       <c r="F48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1646,7 +1641,7 @@
         <v>82</v>
       </c>
       <c r="F49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1666,7 +1661,7 @@
         <v>81</v>
       </c>
       <c r="F50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1683,7 +1678,7 @@
         <v>81</v>
       </c>
       <c r="F51" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1700,7 +1695,7 @@
         <v>81</v>
       </c>
       <c r="F52" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1717,7 +1712,7 @@
         <v>82</v>
       </c>
       <c r="F53" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -1734,7 +1729,7 @@
         <v>82</v>
       </c>
       <c r="F54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -1751,7 +1746,7 @@
         <v>82</v>
       </c>
       <c r="F55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -1771,7 +1766,7 @@
         <v>81</v>
       </c>
       <c r="F56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1788,7 +1783,7 @@
         <v>81</v>
       </c>
       <c r="F57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -1805,7 +1800,7 @@
         <v>81</v>
       </c>
       <c r="F58" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -1822,7 +1817,7 @@
         <v>82</v>
       </c>
       <c r="F59" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -1839,7 +1834,7 @@
         <v>82</v>
       </c>
       <c r="F60" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -1856,7 +1851,7 @@
         <v>82</v>
       </c>
       <c r="F61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -1876,7 +1871,7 @@
         <v>81</v>
       </c>
       <c r="F62" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -1893,7 +1888,7 @@
         <v>81</v>
       </c>
       <c r="F63" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -1910,7 +1905,7 @@
         <v>81</v>
       </c>
       <c r="F64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -1927,7 +1922,7 @@
         <v>82</v>
       </c>
       <c r="F65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -1944,7 +1939,7 @@
         <v>82</v>
       </c>
       <c r="F66" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -1961,7 +1956,7 @@
         <v>82</v>
       </c>
       <c r="F67" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -1981,7 +1976,7 @@
         <v>81</v>
       </c>
       <c r="F68" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2032,7 +2027,7 @@
         <v>82</v>
       </c>
       <c r="F71" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2066,7 +2061,7 @@
         <v>82</v>
       </c>
       <c r="F73" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2086,7 +2081,7 @@
         <v>81</v>
       </c>
       <c r="F74" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2103,7 +2098,7 @@
         <v>81</v>
       </c>
       <c r="F75" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2120,7 +2115,7 @@
         <v>81</v>
       </c>
       <c r="F76" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2137,7 +2132,7 @@
         <v>82</v>
       </c>
       <c r="F77" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2154,7 +2149,7 @@
         <v>82</v>
       </c>
       <c r="F78" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2171,7 +2166,7 @@
         <v>82</v>
       </c>
       <c r="F79" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2191,7 +2186,7 @@
         <v>81</v>
       </c>
       <c r="F80" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2208,7 +2203,7 @@
         <v>81</v>
       </c>
       <c r="F81" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -2225,7 +2220,7 @@
         <v>81</v>
       </c>
       <c r="F82" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2242,7 +2237,7 @@
         <v>82</v>
       </c>
       <c r="F83" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2259,7 +2254,7 @@
         <v>82</v>
       </c>
       <c r="F84" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2276,7 +2271,7 @@
         <v>82</v>
       </c>
       <c r="F85" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2401,7 +2396,7 @@
         <v>81</v>
       </c>
       <c r="F92" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2418,7 +2413,7 @@
         <v>81</v>
       </c>
       <c r="F93" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -2435,7 +2430,7 @@
         <v>81</v>
       </c>
       <c r="F94" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -2452,7 +2447,7 @@
         <v>82</v>
       </c>
       <c r="F95" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -2469,7 +2464,7 @@
         <v>82</v>
       </c>
       <c r="F96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="97" spans="2:6">
@@ -2486,7 +2481,7 @@
         <v>82</v>
       </c>
       <c r="F97" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/matches_data.xlsx
+++ b/data/matches_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17CDE04-23D5-BA4E-9E04-8993322285EC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402D900F-9532-9A4A-95F9-14B18C9334BB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="124">
   <si>
     <t>日期</t>
   </si>
@@ -414,6 +414,10 @@
   </si>
   <si>
     <t>3-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>--</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -862,6 +866,9 @@
       </c>
     </row>
     <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
       <c r="B3" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -882,6 +889,9 @@
       </c>
     </row>
     <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
       <c r="B4" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -902,6 +912,9 @@
       </c>
     </row>
     <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
       <c r="B5" s="2">
         <v>0.8125</v>
       </c>
@@ -922,6 +935,9 @@
       </c>
     </row>
     <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
       <c r="B6" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -942,6 +958,9 @@
       </c>
     </row>
     <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
       <c r="B7" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -980,9 +999,14 @@
       <c r="F8" t="s">
         <v>100</v>
       </c>
-      <c r="G8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
       <c r="B9" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -998,9 +1022,14 @@
       <c r="F9" t="s">
         <v>101</v>
       </c>
-      <c r="G9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
       <c r="B10" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1016,9 +1045,14 @@
       <c r="F10" t="s">
         <v>102</v>
       </c>
-      <c r="G10" s="4"/>
+      <c r="G10" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
       <c r="B11" s="2">
         <v>0.8125</v>
       </c>
@@ -1034,8 +1068,14 @@
       <c r="F11" t="s">
         <v>101</v>
       </c>
+      <c r="G11" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
       <c r="B12" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1051,8 +1091,14 @@
       <c r="F12" t="s">
         <v>102</v>
       </c>
+      <c r="G12" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
       <c r="B13" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1067,6 +1113,9 @@
       </c>
       <c r="F13" t="s">
         <v>103</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1088,8 +1137,14 @@
       <c r="F14" t="s">
         <v>103</v>
       </c>
+      <c r="G14" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
       <c r="B15" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1105,8 +1160,14 @@
       <c r="F15" t="s">
         <v>104</v>
       </c>
+      <c r="G15" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>84</v>
+      </c>
       <c r="B16" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1122,8 +1183,14 @@
       <c r="F16" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
       <c r="B17" s="2">
         <v>0.8125</v>
       </c>
@@ -1139,8 +1206,14 @@
       <c r="F17" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
       <c r="B18" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1156,8 +1229,14 @@
       <c r="F18" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>84</v>
+      </c>
       <c r="B19" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1173,8 +1252,11 @@
       <c r="F19" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>85</v>
       </c>
@@ -1193,8 +1275,14 @@
       <c r="F20" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
       <c r="B21" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1210,8 +1298,14 @@
       <c r="F21" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>85</v>
+      </c>
       <c r="B22" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1227,8 +1321,14 @@
       <c r="F22" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>85</v>
+      </c>
       <c r="B23" s="2">
         <v>0.8125</v>
       </c>
@@ -1244,8 +1344,14 @@
       <c r="F23" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="G23" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>85</v>
+      </c>
       <c r="B24" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1261,8 +1367,14 @@
       <c r="F24" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="G24" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
       <c r="B25" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1278,8 +1390,11 @@
       <c r="F25" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="G25" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>86</v>
       </c>
@@ -1298,8 +1413,14 @@
       <c r="F26" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="G26" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>86</v>
+      </c>
       <c r="B27" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1315,8 +1436,14 @@
       <c r="F27" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="G27" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>86</v>
+      </c>
       <c r="B28" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1332,8 +1459,14 @@
       <c r="F28" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="G28" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>86</v>
+      </c>
       <c r="B29" s="2">
         <v>0.8125</v>
       </c>
@@ -1349,8 +1482,14 @@
       <c r="F29" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="G29" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>86</v>
+      </c>
       <c r="B30" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1366,8 +1505,14 @@
       <c r="F30" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="G30" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>86</v>
+      </c>
       <c r="B31" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1383,8 +1528,11 @@
       <c r="F31" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="G31" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -1403,8 +1551,14 @@
       <c r="F32" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="G32" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>87</v>
+      </c>
       <c r="B33" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1420,8 +1574,14 @@
       <c r="F33" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="G33" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>87</v>
+      </c>
       <c r="B34" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1437,8 +1597,14 @@
       <c r="F34" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="G34" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>87</v>
+      </c>
       <c r="B35" s="2">
         <v>0.8125</v>
       </c>
@@ -1454,8 +1620,14 @@
       <c r="F35" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="G35" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>87</v>
+      </c>
       <c r="B36" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1471,8 +1643,14 @@
       <c r="F36" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="G36" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>87</v>
+      </c>
       <c r="B37" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1488,8 +1666,11 @@
       <c r="F37" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="G37" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -1508,8 +1689,14 @@
       <c r="F38" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="G38" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>89</v>
+      </c>
       <c r="B39" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1525,8 +1712,14 @@
       <c r="F39" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="G39" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>89</v>
+      </c>
       <c r="B40" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1542,8 +1735,14 @@
       <c r="F40" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="G40" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>89</v>
+      </c>
       <c r="B41" s="2">
         <v>0.8125</v>
       </c>
@@ -1559,8 +1758,14 @@
       <c r="F41" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="G41" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>89</v>
+      </c>
       <c r="B42" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1576,8 +1781,14 @@
       <c r="F42" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="G42" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>89</v>
+      </c>
       <c r="B43" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1593,8 +1804,11 @@
       <c r="F43" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="G43" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>90</v>
       </c>
@@ -1613,8 +1827,14 @@
       <c r="F44" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="G44" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>90</v>
+      </c>
       <c r="B45" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1630,8 +1850,14 @@
       <c r="F45" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="G45" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>90</v>
+      </c>
       <c r="B46" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1647,8 +1873,14 @@
       <c r="F46" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="47" spans="1:6">
+      <c r="G46" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>90</v>
+      </c>
       <c r="B47" s="2">
         <v>0.8125</v>
       </c>
@@ -1664,8 +1896,14 @@
       <c r="F47" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="G47" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>90</v>
+      </c>
       <c r="B48" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1681,8 +1919,14 @@
       <c r="F48" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="G48" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>90</v>
+      </c>
       <c r="B49" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1698,8 +1942,11 @@
       <c r="F49" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="50" spans="1:6">
+      <c r="G49" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>91</v>
       </c>
@@ -1718,8 +1965,14 @@
       <c r="F50" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="G50" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>91</v>
+      </c>
       <c r="B51" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1735,8 +1988,14 @@
       <c r="F51" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="G51" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>91</v>
+      </c>
       <c r="B52" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1752,8 +2011,14 @@
       <c r="F52" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="53" spans="1:6">
+      <c r="G52" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>91</v>
+      </c>
       <c r="B53" s="2">
         <v>0.8125</v>
       </c>
@@ -1769,8 +2034,14 @@
       <c r="F53" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="G53" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>91</v>
+      </c>
       <c r="B54" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1786,8 +2057,14 @@
       <c r="F54" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="55" spans="1:6">
+      <c r="G54" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>91</v>
+      </c>
       <c r="B55" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1803,8 +2080,11 @@
       <c r="F55" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="G55" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>92</v>
       </c>
@@ -1823,8 +2103,14 @@
       <c r="F56" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="G56" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>92</v>
+      </c>
       <c r="B57" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1840,8 +2126,14 @@
       <c r="F57" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="58" spans="1:6">
+      <c r="G57" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>92</v>
+      </c>
       <c r="B58" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1857,8 +2149,14 @@
       <c r="F58" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="59" spans="1:6">
+      <c r="G58" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>92</v>
+      </c>
       <c r="B59" s="2">
         <v>0.8125</v>
       </c>
@@ -1874,8 +2172,14 @@
       <c r="F59" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="G59" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>92</v>
+      </c>
       <c r="B60" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1891,8 +2195,14 @@
       <c r="F60" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="G60" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>92</v>
+      </c>
       <c r="B61" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1908,8 +2218,11 @@
       <c r="F61" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="G61" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>93</v>
       </c>
@@ -1928,8 +2241,14 @@
       <c r="F62" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="63" spans="1:6">
+      <c r="G62" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>93</v>
+      </c>
       <c r="B63" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1945,8 +2264,14 @@
       <c r="F63" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="G63" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>93</v>
+      </c>
       <c r="B64" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -1962,8 +2287,14 @@
       <c r="F64" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="G64" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>93</v>
+      </c>
       <c r="B65" s="2">
         <v>0.8125</v>
       </c>
@@ -1979,8 +2310,14 @@
       <c r="F65" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="G65" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>93</v>
+      </c>
       <c r="B66" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -1996,8 +2333,14 @@
       <c r="F66" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="G66" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>93</v>
+      </c>
       <c r="B67" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -2013,8 +2356,11 @@
       <c r="F67" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="G67" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>94</v>
       </c>
@@ -2033,8 +2379,14 @@
       <c r="F68" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="69" spans="1:6">
+      <c r="G68" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>94</v>
+      </c>
       <c r="B69" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -2050,8 +2402,14 @@
       <c r="F69" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="70" spans="1:6">
+      <c r="G69" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>94</v>
+      </c>
       <c r="B70" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -2067,8 +2425,14 @@
       <c r="F70" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="71" spans="1:6">
+      <c r="G70" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
+        <v>94</v>
+      </c>
       <c r="B71" s="2">
         <v>0.8125</v>
       </c>
@@ -2084,8 +2448,14 @@
       <c r="F71" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="72" spans="1:6">
+      <c r="G71" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>94</v>
+      </c>
       <c r="B72" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -2101,8 +2471,14 @@
       <c r="F72" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="73" spans="1:6">
+      <c r="G72" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>94</v>
+      </c>
       <c r="B73" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -2118,8 +2494,11 @@
       <c r="F73" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="G73" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>95</v>
       </c>
@@ -2138,8 +2517,14 @@
       <c r="F74" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="75" spans="1:6">
+      <c r="G74" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>95</v>
+      </c>
       <c r="B75" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -2155,8 +2540,14 @@
       <c r="F75" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="G75" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>95</v>
+      </c>
       <c r="B76" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -2172,8 +2563,14 @@
       <c r="F76" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="77" spans="1:6">
+      <c r="G76" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>95</v>
+      </c>
       <c r="B77" s="2">
         <v>0.8125</v>
       </c>
@@ -2189,8 +2586,14 @@
       <c r="F77" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="G77" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>95</v>
+      </c>
       <c r="B78" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -2206,8 +2609,14 @@
       <c r="F78" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="79" spans="1:6">
+      <c r="G78" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>95</v>
+      </c>
       <c r="B79" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -2223,8 +2632,11 @@
       <c r="F79" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="80" spans="1:6">
+      <c r="G79" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
         <v>96</v>
       </c>
@@ -2243,8 +2655,14 @@
       <c r="F80" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="81" spans="1:6">
+      <c r="G80" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
+        <v>96</v>
+      </c>
       <c r="B81" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -2260,8 +2678,14 @@
       <c r="F81" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="82" spans="1:6">
+      <c r="G81" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" t="s">
+        <v>96</v>
+      </c>
       <c r="B82" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -2277,8 +2701,14 @@
       <c r="F82" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="G82" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
+        <v>96</v>
+      </c>
       <c r="B83" s="2">
         <v>0.8125</v>
       </c>
@@ -2294,8 +2724,14 @@
       <c r="F83" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="84" spans="1:6">
+      <c r="G83" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
+        <v>96</v>
+      </c>
       <c r="B84" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -2311,8 +2747,14 @@
       <c r="F84" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="85" spans="1:6">
+      <c r="G84" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" t="s">
+        <v>96</v>
+      </c>
       <c r="B85" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -2328,8 +2770,11 @@
       <c r="F85" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="86" spans="1:6">
+      <c r="G85" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2348,8 +2793,14 @@
       <c r="F86" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="87" spans="1:6">
+      <c r="G86" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" t="s">
+        <v>97</v>
+      </c>
       <c r="B87" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -2365,8 +2816,14 @@
       <c r="F87" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="88" spans="1:6">
+      <c r="G87" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" t="s">
+        <v>97</v>
+      </c>
       <c r="B88" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -2382,8 +2839,14 @@
       <c r="F88" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="89" spans="1:6">
+      <c r="G88" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>97</v>
+      </c>
       <c r="B89" s="2">
         <v>0.8125</v>
       </c>
@@ -2399,8 +2862,14 @@
       <c r="F89" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:6">
+      <c r="G89" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
+        <v>97</v>
+      </c>
       <c r="B90" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -2416,8 +2885,14 @@
       <c r="F90" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="91" spans="1:6">
+      <c r="G90" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
+        <v>97</v>
+      </c>
       <c r="B91" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -2433,8 +2908,11 @@
       <c r="F91" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="G91" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
         <v>98</v>
       </c>
@@ -2453,8 +2931,14 @@
       <c r="F92" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="93" spans="1:6">
+      <c r="G92" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" t="s">
+        <v>98</v>
+      </c>
       <c r="B93" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -2470,8 +2954,14 @@
       <c r="F93" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="94" spans="1:6">
+      <c r="G93" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
+        <v>98</v>
+      </c>
       <c r="B94" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -2487,8 +2977,14 @@
       <c r="F94" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="95" spans="1:6">
+      <c r="G94" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" t="s">
+        <v>98</v>
+      </c>
       <c r="B95" s="2">
         <v>0.8125</v>
       </c>
@@ -2504,8 +3000,14 @@
       <c r="F95" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="96" spans="1:6">
+      <c r="G95" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
+        <v>98</v>
+      </c>
       <c r="B96" s="2">
         <v>0.85416666666666663</v>
       </c>
@@ -2521,8 +3023,14 @@
       <c r="F96" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="97" spans="2:6">
+      <c r="G96" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
+        <v>98</v>
+      </c>
       <c r="B97" s="2">
         <v>0.89583333333333337</v>
       </c>
@@ -2537,6 +3045,9 @@
       </c>
       <c r="F97" t="s">
         <v>108</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/data/matches_data.xlsx
+++ b/data/matches_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402D900F-9532-9A4A-95F9-14B18C9334BB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE93D92F-F637-0A44-A44C-0FE55EDE5D7A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
@@ -26,6 +26,9 @@
     <sheet name="中年組_積分榜" sheetId="12" r:id="rId11"/>
     <sheet name="元老組_積分榜" sheetId="13" r:id="rId12"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">初級組_對賽安排!$A$1:$G$97</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -803,18 +806,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16E0EA83-C783-7140-AD8B-B43A843048C1}">
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="34.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="33.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="36.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -836,13 +840,13 @@
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
+      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>80</v>
       </c>
@@ -865,7 +869,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -888,7 +892,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>80</v>
       </c>
@@ -911,7 +915,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>80</v>
       </c>
@@ -934,7 +938,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -957,7 +961,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -980,7 +984,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>83</v>
       </c>
@@ -1003,7 +1007,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -1026,7 +1030,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>83</v>
       </c>
@@ -1049,7 +1053,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>83</v>
       </c>
@@ -1072,7 +1076,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>83</v>
       </c>
@@ -1095,7 +1099,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
         <v>83</v>
       </c>
@@ -1118,7 +1122,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
         <v>84</v>
       </c>
@@ -1141,7 +1145,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
         <v>84</v>
       </c>
@@ -1164,7 +1168,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
         <v>84</v>
       </c>
@@ -3051,6 +3055,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G97" xr:uid="{5669F9CD-EFBC-0241-9CC1-59B229E01A6E}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/matches_data.xlsx
+++ b/data/matches_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE93D92F-F637-0A44-A44C-0FE55EDE5D7A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17049E2-6570-0D4F-B23B-6FBEE60002AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
@@ -17,14 +17,6 @@
     <sheet name="高級組_對賽安排" sheetId="3" r:id="rId2"/>
     <sheet name="中年組_對賽安排" sheetId="4" r:id="rId3"/>
     <sheet name="元老組_對賽安排" sheetId="5" r:id="rId4"/>
-    <sheet name="初級組_對賽成績" sheetId="6" r:id="rId5"/>
-    <sheet name="高級組_對賽成績" sheetId="7" r:id="rId6"/>
-    <sheet name="中年組_對賽成績" sheetId="8" r:id="rId7"/>
-    <sheet name="元老組_對賽成績" sheetId="9" r:id="rId8"/>
-    <sheet name="初級組_積分榜" sheetId="10" r:id="rId9"/>
-    <sheet name="高級組_積分榜" sheetId="11" r:id="rId10"/>
-    <sheet name="中年組_積分榜" sheetId="12" r:id="rId11"/>
-    <sheet name="元老組_積分榜" sheetId="13" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">初級組_對賽安排!$A$1:$G$97</definedName>
@@ -3061,36 +3053,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3F7A55-04D4-B04B-84FF-591FF4F614D9}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4AC8762-985C-3A44-B364-81DD41A51242}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D79C342-754F-004C-BF28-9C2A6F616F90}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A652382C-1B8E-3D47-8B07-5935E173CD82}">
   <dimension ref="A1"/>
@@ -3119,54 +3081,4 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458C2E21-9836-DA4F-827E-3FCC599A483F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C9A1FC-F4CC-684F-B555-3819BBE99676}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{380B5DAA-237F-AA4C-8E6D-5F833856F631}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D35C9D81-3C0C-184B-A871-A36329AF0312}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F41BCBC-A307-E74C-9A70-3056FE7E3E56}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>